--- a/S1-prior_checklist.xlsx
+++ b/S1-prior_checklist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\drive_gmail\Recherche\Article 2 - Base de Donnees\3 - Extraction CAM\8 - article\Submission\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\drive_gmail\Recherche\Article 34 - EBI-ADHD\data_analysis\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BB82BF-1C16-44DD-9E6D-BAD6017AE266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD72F7EE-B4EC-42B6-8427-400EB12F264C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{0A664963-3F39-41FC-9A14-3324B0B99935}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{0A664963-3F39-41FC-9A14-3324B0B99935}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="143">
   <si>
     <t>Title</t>
   </si>
@@ -257,9 +257,6 @@
     <t>Identify the report as an overview of reviews</t>
   </si>
   <si>
-    <t>we identified it as large-scale synthesis in the title as the term overview/umbrella review is not know by all readers, and more clearly as umbrella review in abstract</t>
-  </si>
-  <si>
     <t>abstract</t>
   </si>
   <si>
@@ -269,36 +266,18 @@
     <t>last paragraph of the introduction</t>
   </si>
   <si>
-    <t>paragraph entitled 'Search strategy and eligibility criteria '</t>
-  </si>
-  <si>
-    <t>paragraph entitled 'Overlapping meta-analyses'</t>
-  </si>
-  <si>
     <t>paragraph entitled 'Data extraction and checking'</t>
   </si>
   <si>
-    <t>paragraphs entitled 'Data extraction and checking' and 'Overlapping meta-analyses'</t>
-  </si>
-  <si>
     <t>not applicable, we selected 1 SR/MA per PICO</t>
   </si>
   <si>
-    <t>paragraph entitled 'Assessment of the methodological quality'</t>
-  </si>
-  <si>
     <t>not applicable</t>
   </si>
   <si>
     <t>paragraph entitled 'Assessment of the certainty of evidence'</t>
   </si>
   <si>
-    <t>paragraph entitled ''</t>
-  </si>
-  <si>
-    <t>paragraph entitled 'Data analysis '</t>
-  </si>
-  <si>
     <t>Results</t>
   </si>
   <si>
@@ -416,56 +395,83 @@
     <t>Describe the results of the search and selection process, including the number of records screened, assessed for eligibility, and included in the overview of reviews, ideally with a flow diagram.</t>
   </si>
   <si>
-    <t>paragraph entitled 'Results of the searches.'</t>
-  </si>
-  <si>
-    <t>paragraph entitled ''Characteristics of the meta-analytic reports retained in the umbrella review" + Supplementary materials</t>
-  </si>
-  <si>
     <t>Supplementary materials</t>
   </si>
   <si>
     <t>not applicable, because we removed reports that combined several intervention types</t>
   </si>
   <si>
-    <t>paragraph entitled ''Description of the meta-analyses included in the primary analysis" + Supplementary materials</t>
-  </si>
-  <si>
-    <t>paragraph entitled ''Results of our primary analysis" + Supplementary materials</t>
-  </si>
-  <si>
     <t>not applicable (moderators are not consistently reported across meta-analyses)</t>
   </si>
   <si>
-    <t>Supplementary materials (e.g., sensitivity analysis excluding NRCT)</t>
-  </si>
-  <si>
-    <t>paragraph entitled ''Results of our primary analysis" + "Overlapping meta-analyses" + Supplementary materials</t>
-  </si>
-  <si>
     <t>Discussion section</t>
   </si>
   <si>
-    <t>Title page (prospero number)</t>
-  </si>
-  <si>
     <t>paragraph entitled ''Funding. "</t>
   </si>
   <si>
     <t>paragraph entitled ''Conflict of Interest. "</t>
   </si>
   <si>
-    <t>online manager</t>
-  </si>
-  <si>
     <t>All raw data are available : "Data availability. "</t>
+  </si>
+  <si>
+    <t>we identified it as umbrella review</t>
+  </si>
+  <si>
+    <t>paragraph entitled 'Search strategy and eligibility criteria' + supplementary materials</t>
+  </si>
+  <si>
+    <t>Supplementary Materials S4</t>
+  </si>
+  <si>
+    <t>not applicable, we selected 1 SR/MA per PICO + Supplementary Materials S4</t>
+  </si>
+  <si>
+    <t>paragraph entitled 'Search strategy and eligibility criteria ' + Supplementary Materials S5</t>
+  </si>
+  <si>
+    <t>paragraph entitled 'Assessment of the methodological quality of primary studies and meta-analyses'</t>
+  </si>
+  <si>
+    <t>paragraph entitled 'Data analysis ' + Supplementary Materials S5</t>
+  </si>
+  <si>
+    <t>first paragraph of the results</t>
+  </si>
+  <si>
+    <t>paragraph entitled ''Characteristics of the meta-analytic reports retained in the umbrella review" + Supplementary materials S8</t>
+  </si>
+  <si>
+    <t>paragraph entitled ''Characteristics of the meta-analyses retained in the umbrella review" + Supplementary materials S10</t>
+  </si>
+  <si>
+    <t>paragraph entitled ''Characteristics of the meta-analyses retained in the umbrella review" + Supplementary materials</t>
+  </si>
+  <si>
+    <t>paragraphs entitled "Primary outcomes" and "Secondary outcomes" + Supplementary Materials</t>
+  </si>
+  <si>
+    <t>paragraph entitled "Sensitivity analysis" + Supplementary Materials</t>
+  </si>
+  <si>
+    <t>Title page (osf URL)</t>
+  </si>
+  <si>
+    <t>Supplementary materials S2</t>
+  </si>
+  <si>
+    <t>Title page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paragraph entitled "Author's contribution" </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -479,6 +485,14 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -501,13 +515,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -844,810 +865,812 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D44154-26A7-4BFB-AD81-3B8C7BCD927E}">
   <dimension ref="A1:I47"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="4" max="4" width="70.88671875" customWidth="1"/>
+    <col min="2" max="2" width="21.90625" customWidth="1"/>
+    <col min="3" max="3" width="10.90625" style="5"/>
+    <col min="4" max="4" width="55.36328125" customWidth="1"/>
+    <col min="5" max="5" width="104.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
         <v>0</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="5">
         <v>1</v>
       </c>
       <c r="D2" t="s">
         <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="5">
         <v>2</v>
       </c>
       <c r="D3" t="s">
         <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="5">
         <v>3</v>
       </c>
       <c r="D4" t="s">
         <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>20</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
         <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D6" t="s">
         <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>21</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D7" t="s">
         <v>66</v>
       </c>
       <c r="E7" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>21</v>
       </c>
       <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="5">
         <v>6</v>
       </c>
       <c r="D8" t="s">
         <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="5">
         <v>7</v>
       </c>
       <c r="D9" t="s">
         <v>64</v>
       </c>
       <c r="E9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>21</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D10" t="s">
         <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>21</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D11" t="s">
         <v>62</v>
       </c>
       <c r="E11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>21</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
         <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D13" t="s">
         <v>60</v>
       </c>
       <c r="E13" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>21</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="5" t="s">
         <v>68</v>
       </c>
       <c r="D14" t="s">
         <v>59</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>21</v>
       </c>
       <c r="B15" t="s">
         <v>22</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="5">
         <v>10</v>
       </c>
       <c r="D15" t="s">
         <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D16" t="s">
         <v>57</v>
       </c>
       <c r="E16" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>21</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D17" t="s">
         <v>56</v>
       </c>
       <c r="E17" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D18" t="s">
         <v>55</v>
       </c>
       <c r="E18" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>21</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D19" t="s">
         <v>54</v>
       </c>
       <c r="E19" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20" t="s">
         <v>47</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D20" t="s">
         <v>53</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>21</v>
       </c>
       <c r="B21" t="s">
         <v>47</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D21" t="s">
         <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
       <c r="B22" t="s">
         <v>48</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="5">
         <v>13</v>
       </c>
       <c r="D22" t="s">
         <v>51</v>
       </c>
       <c r="E22" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>21</v>
       </c>
       <c r="B23" t="s">
         <v>49</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="5">
         <v>14</v>
       </c>
       <c r="D23" t="s">
         <v>50</v>
       </c>
       <c r="E23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="5">
+        <v>16</v>
+      </c>
+      <c r="D26" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="5">
+        <v>17</v>
+      </c>
+      <c r="D27" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="C28" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" t="s">
+        <v>84</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" t="s">
+        <v>112</v>
+      </c>
+      <c r="E30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" t="s">
+        <v>110</v>
+      </c>
+      <c r="E32" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>80</v>
+      </c>
+      <c r="B33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" t="s">
+        <v>109</v>
+      </c>
+      <c r="E33" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="5">
+        <v>20</v>
+      </c>
+      <c r="D34" t="s">
+        <v>108</v>
+      </c>
+      <c r="E34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" t="s">
         <v>87</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C35" s="5">
+        <v>21</v>
+      </c>
+      <c r="D35" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>88</v>
       </c>
-      <c r="C24" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="B36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" t="s">
+        <v>106</v>
+      </c>
+      <c r="E36" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>88</v>
+      </c>
+      <c r="B37" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" t="s">
+        <v>105</v>
+      </c>
+      <c r="E37" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" t="s">
+        <v>103</v>
+      </c>
+      <c r="E39" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" t="s">
+        <v>101</v>
+      </c>
+      <c r="E41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>89</v>
+      </c>
+      <c r="B42" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" t="s">
+        <v>100</v>
+      </c>
+      <c r="E42" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="5">
+        <v>24</v>
+      </c>
+      <c r="D43" t="s">
+        <v>99</v>
+      </c>
+      <c r="E43" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>89</v>
+      </c>
+      <c r="B44" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="5">
+        <v>25</v>
+      </c>
+      <c r="D44" t="s">
+        <v>98</v>
+      </c>
+      <c r="E44" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" t="s">
+        <v>97</v>
+      </c>
+      <c r="E45" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" t="s">
+        <v>96</v>
+      </c>
+      <c r="E46" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>89</v>
+      </c>
+      <c r="B47" t="s">
+        <v>94</v>
+      </c>
+      <c r="C47" s="5">
+        <v>26</v>
+      </c>
+      <c r="D47" t="s">
+        <v>95</v>
+      </c>
+      <c r="E47" t="s">
         <v>125</v>
-      </c>
-      <c r="E24" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" t="s">
-        <v>124</v>
-      </c>
-      <c r="E25" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>87</v>
-      </c>
-      <c r="B26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26">
-        <v>16</v>
-      </c>
-      <c r="D26" t="s">
-        <v>123</v>
-      </c>
-      <c r="E26" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>87</v>
-      </c>
-      <c r="B27" t="s">
-        <v>90</v>
-      </c>
-      <c r="C27">
-        <v>17</v>
-      </c>
-      <c r="D27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>87</v>
-      </c>
-      <c r="B28" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" t="s">
-        <v>121</v>
-      </c>
-      <c r="E28" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>87</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" t="s">
-        <v>120</v>
-      </c>
-      <c r="E29" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>87</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" t="s">
-        <v>119</v>
-      </c>
-      <c r="E30" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>87</v>
-      </c>
-      <c r="B32" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" t="s">
-        <v>117</v>
-      </c>
-      <c r="E32" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>87</v>
-      </c>
-      <c r="B33" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" t="s">
-        <v>37</v>
-      </c>
-      <c r="D33" t="s">
-        <v>116</v>
-      </c>
-      <c r="E33" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C34">
-        <v>20</v>
-      </c>
-      <c r="D34" t="s">
-        <v>115</v>
-      </c>
-      <c r="E34" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" t="s">
-        <v>94</v>
-      </c>
-      <c r="C35">
-        <v>21</v>
-      </c>
-      <c r="D35" t="s">
-        <v>114</v>
-      </c>
-      <c r="E35" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>95</v>
-      </c>
-      <c r="B36" t="s">
-        <v>95</v>
-      </c>
-      <c r="C36" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>95</v>
-      </c>
-      <c r="B37" t="s">
-        <v>95</v>
-      </c>
-      <c r="C37" t="s">
-        <v>39</v>
-      </c>
-      <c r="D37" t="s">
-        <v>112</v>
-      </c>
-      <c r="E37" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>95</v>
-      </c>
-      <c r="B38" t="s">
-        <v>95</v>
-      </c>
-      <c r="C38" t="s">
-        <v>40</v>
-      </c>
-      <c r="D38" t="s">
-        <v>111</v>
-      </c>
-      <c r="E38" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>95</v>
-      </c>
-      <c r="B39" t="s">
-        <v>95</v>
-      </c>
-      <c r="C39" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39" t="s">
-        <v>110</v>
-      </c>
-      <c r="E39" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>96</v>
-      </c>
-      <c r="B40" t="s">
-        <v>97</v>
-      </c>
-      <c r="C40" t="s">
-        <v>42</v>
-      </c>
-      <c r="D40" t="s">
-        <v>109</v>
-      </c>
-      <c r="E40" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" t="s">
-        <v>108</v>
-      </c>
-      <c r="E41" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>96</v>
-      </c>
-      <c r="B42" t="s">
-        <v>97</v>
-      </c>
-      <c r="C42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" t="s">
-        <v>107</v>
-      </c>
-      <c r="E42" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>96</v>
-      </c>
-      <c r="B43" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43">
-        <v>24</v>
-      </c>
-      <c r="D43" t="s">
-        <v>106</v>
-      </c>
-      <c r="E43" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>96</v>
-      </c>
-      <c r="B44" t="s">
-        <v>99</v>
-      </c>
-      <c r="C44">
-        <v>25</v>
-      </c>
-      <c r="D44" t="s">
-        <v>105</v>
-      </c>
-      <c r="E44" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>96</v>
-      </c>
-      <c r="B45" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" t="s">
-        <v>45</v>
-      </c>
-      <c r="D45" t="s">
-        <v>104</v>
-      </c>
-      <c r="E45" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>96</v>
-      </c>
-      <c r="B46" t="s">
-        <v>100</v>
-      </c>
-      <c r="C46" t="s">
-        <v>46</v>
-      </c>
-      <c r="D46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E46" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>96</v>
-      </c>
-      <c r="B47" t="s">
-        <v>101</v>
-      </c>
-      <c r="C47">
-        <v>26</v>
-      </c>
-      <c r="D47" t="s">
-        <v>102</v>
-      </c>
-      <c r="E47" t="s">
-        <v>140</v>
       </c>
     </row>
   </sheetData>
